--- a/theory/bem.xlsx
+++ b/theory/bem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louis\source\repos\propeller-acoustics\theory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA476FDD-5DC4-49F2-8260-7498792A4F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA89939B-8324-4814-A162-03102AB39004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{9A8C249E-654E-4DF1-B1BC-4F0B7C8B2B3E}"/>
   </bookViews>
